--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avverkningsanmälningar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anmälningar" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,11 +420,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
-  </cols>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
     <row r="1" ht="15" customHeight="1">
@@ -435,125 +432,140 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Åtgärd</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Förändrad</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Län</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Kommun</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Markägare</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Area (ha)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Fridlysta</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Signalarter</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>NT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>VU</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>RE</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Rödlistade</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Hotade</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Alla arter</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Antal fynd</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>Artnamn</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Artfyndslänk</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Kartlänk</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Knärotsbuffertlänk</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Klagomålslänk</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Klagomålsmaillänk</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Tillsynsbegäranslänk</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Tillsynsbegäransmaillänk</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
         </is>
@@ -567,58 +579,75 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>45508</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Norrbottens län</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Arvidsjaur</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>203.2</v>
       </c>
-      <c r="H2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I2" t="n">
-        <v>17</v>
-      </c>
       <c r="J2" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L2" t="n">
+        <v>37</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>70</v>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
+        <v>48</v>
+      </c>
+      <c r="R2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S2" t="n">
+        <v>73</v>
+      </c>
+      <c r="T2" t="n">
+        <v>891</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Urskogsporing
 Blackticka
 Doftticka
 Fläckporing
+Garnlav
 Gräddporing
+Gränsticka
 Knärot
 Lateritticka
 Smalfotad taggsvamp
@@ -629,18 +658,16 @@
 Blågrå svartspik
 Brunpudrad nållav
 Doftskinn
+Dropptaggsvamp
 Dvärgbägarlav
 Gammelgransskål
-Garnlav
-Granticka
-Gränsticka
 Grå blåbärsfältmätare
 Hornvaxskinn
-Järpe
 Knottrig blåslav
 Kolflarnlav
 Kortskaftad ärgspik
 Kådvaxskinn
+Lavskrika
 Liten svartspik
 Luddfingersvamp
 Lunglav
@@ -648,8 +675,9 @@
 Nordtagging
 Orange taggsvamp
 Rosenticka
-Spillkråka
-Svart taggsvamp
+Rostania effusa
+Skarp dropptaggsvamp
+Talltagel
 Tallticka
 Talltita
 Tretåig hackspett
@@ -663,58 +691,60 @@
 Vitplätt
 Blodticka
 Bårdlav
-Dropptaggsvamp
 Jättesvampmal
 Källpraktmossa
 Luddlav
 Norrlandslav
 Nästlav
 Plattlummer
-Skarp dropptaggsvamp
 Skinnlav
 Sotlav
 Spindelblomster
 Stuplav
+Trådticka
 Vedticka
 Vågbandad barkbock
 Ögonpyrola
+Järpe
+Spillkråka
+Tjäder
 Kungsfågel
-Lavskrika
-Tjäder
+Orre
+Huggorm
 Vanlig groda
 Fläcknycklar
 Revlummer</t>
         </is>
       </c>
-      <c r="S2">
+      <c r="V2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Östra Luspenåivve artfynd.xlsx", "Östra Luspenåivve")</f>
         <v/>
       </c>
-      <c r="T2">
+      <c r="W2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Östra Luspenåivve karta.png", "Östra Luspenåivve")</f>
         <v/>
       </c>
-      <c r="U2">
+      <c r="X2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/knärot/Östra Luspenåivve karta knärot.png", "Östra Luspenåivve")</f>
         <v/>
       </c>
-      <c r="V2">
+      <c r="Y2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Östra Luspenåivve FSC-klagomål.docx", "Östra Luspenåivve")</f>
         <v/>
       </c>
-      <c r="W2">
+      <c r="Z2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Östra Luspenåivve FSC-klagomål mail.docx", "Östra Luspenåivve")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="AA2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Östra Luspenåivve tillsynsbegäran.docx", "Östra Luspenåivve")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="AB2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Östra Luspenåivve tillsynsbegäran mail.docx", "Östra Luspenåivve")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="AC2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Östra Luspenåivve prioriterade fågelarter.docx", "Östra Luspenåivve")</f>
         <v/>
       </c>
@@ -727,77 +757,97 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>45508</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Norrbottens län</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Arvidsjaur</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>132</v>
       </c>
-      <c r="H3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I3" t="n">
-        <v>14</v>
-      </c>
       <c r="J3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" t="n">
         <v>30</v>
       </c>
-      <c r="K3" t="n">
-        <v>13</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>60</v>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>Urskogsporing
+        <v>49</v>
+      </c>
+      <c r="R3" t="n">
+        <v>19</v>
+      </c>
+      <c r="S3" t="n">
+        <v>65</v>
+      </c>
+      <c r="T3" t="n">
+        <v>436</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>Lusporing
+Phellodon resupinatus
+Urskogsporing
 Borsttagging
 Doftticka
 Fläckporing
 Gräddporing
 Gräddticka
+Gränsticka
 Knärot
 Kristallticka
 Lateritticka
 Laxgröppa
 Laxporing
+Lecidea subhumida
 Norna
 Smalfotad taggsvamp
 Tallstocksticka
+Timmerskapania
 Blanksvart spiklav
 Blå taggsvamp
 Blågrå svartspik
+Dropptaggsvamp
 Dvärgbägarlav
-Granticka
-Gränsticka
 Hornvaxskinn
 Knottrig blåslav
 Kolflarnlav
 Kortskaftad ärgspik
+Lavskrika
 Luddfingersvamp
 Lunglav
 Mörk kolflarnlav
@@ -806,8 +856,8 @@
 Rosenticka
 Röd trolldruva
 Skrovellav
-Spillkråka
 Svartvit taggsvamp
+Talltagel
 Tallticka
 Talltita
 Tretåig hackspett
@@ -820,11 +870,12 @@
 Vitplätt
 Blodticka
 Bårdlav
-Dropptaggsvamp
 Dvärgtufs
 Gytterlav
 Korallblylav
 Luddlav
+Norrlandslav
+Nästlav
 Plattlummer
 Skinnlav
 Spindelblomster
@@ -832,39 +883,38 @@
 Svart trolldruva
 Vedticka
 Ögonpyrola
-Lavskrika
-Tjäder</t>
-        </is>
-      </c>
-      <c r="S3">
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="V3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Björnideforsen C artfynd.xlsx", "Björnideforsen C")</f>
         <v/>
       </c>
-      <c r="T3">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Björnideforsen C karta.png", "Björnideforsen C")</f>
         <v/>
       </c>
-      <c r="U3">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/knärot/Björnideforsen C karta knärot.png", "Björnideforsen C")</f>
         <v/>
       </c>
-      <c r="V3">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Björnideforsen C FSC-klagomål.docx", "Björnideforsen C")</f>
         <v/>
       </c>
-      <c r="W3">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Björnideforsen C FSC-klagomål mail.docx", "Björnideforsen C")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Björnideforsen C tillsynsbegäran.docx", "Björnideforsen C")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Björnideforsen C tillsynsbegäran mail.docx", "Björnideforsen C")</f>
         <v/>
       </c>
-      <c r="Z3">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Björnideforsen C prioriterade fågelarter.docx", "Björnideforsen C")</f>
         <v/>
       </c>
@@ -877,81 +927,98 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>45508</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Norrbottens län</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Arvidsjaur</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>61.3</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>13</v>
       </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>31</v>
-      </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>56</v>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
+        <v>38</v>
+      </c>
+      <c r="R4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S4" t="n">
+        <v>57</v>
+      </c>
+      <c r="T4" t="n">
+        <v>290</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Fläckporing
+Garnlav
 Gräddporing
+Gränsticka
 Knärot
 Lappticka
+Lecidea subhumida
+Mospindling
+Skrovlig taggsvamp
 Blanksvart spiklav
 Blågrå svartspik
+Dropptaggsvamp
 Dvärgbägarlav
 Gammelgransskål
-Garnlav
-Granticka
-Gränsticka
 Grå blåbärsfältmätare
 Harticka
 Hornvaxskinn
-Järpe
 Knottrig blåslav
 Kolflarnlav
 Kortskaftad ärgspik
+Lavskrika
 Lunglav
-Mospindling
 Mörk kolflarnlav
 Nordtagging
 Rosenticka
+Skarp dropptaggsvamp
 Skrovellav
-Skrovlig taggsvamp
-Spillkråka
 Stjärntagging
+Talltagel
 Talltita
 Tretåig hackspett
 Ullticka
@@ -962,55 +1029,54 @@
 Vitplätt
 Bronshjon
 Bårdlav
-Dropptaggsvamp
 Korallrot
 Luddlav
 Mörk husmossa
 Norrlandslav
 Nästlav
 Plattlummer
-Skarp dropptaggsvamp
 Skinnlav
 Spindelblomster
 Stuplav
 Trådticka
 Vedticka
 Ögonpyrola
-Lavskrika
+Järpe
+Spillkråka
 Tjäder
 Fläcknycklar
 Revlummer</t>
         </is>
       </c>
-      <c r="S4">
+      <c r="V4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Slaktarberget artfynd.xlsx", "Slaktarberget")</f>
         <v/>
       </c>
-      <c r="T4">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Slaktarberget karta.png", "Slaktarberget")</f>
         <v/>
       </c>
-      <c r="U4">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/knärot/Slaktarberget karta knärot.png", "Slaktarberget")</f>
         <v/>
       </c>
-      <c r="V4">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Slaktarberget FSC-klagomål.docx", "Slaktarberget")</f>
         <v/>
       </c>
-      <c r="W4">
+      <c r="Z4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Slaktarberget FSC-klagomål mail.docx", "Slaktarberget")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Slaktarberget tillsynsbegäran.docx", "Slaktarberget")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Slaktarberget tillsynsbegäran mail.docx", "Slaktarberget")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Slaktarberget prioriterade fågelarter.docx", "Slaktarberget")</f>
         <v/>
       </c>
@@ -1023,76 +1089,92 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>45508</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Norrbottens län</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Arvidsjaur</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>98.5</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>12</v>
       </c>
-      <c r="I5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J5" t="n">
-        <v>28</v>
-      </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
+        <v>34</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7</v>
+      </c>
+      <c r="S5" t="n">
         <v>52</v>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="T5" t="n">
+        <v>285</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
+Garnlav
 Gräddporing
+Gränsticka
 Liten sotlav
 Narrporing
 Tajgaskinn
 Blanksvart spiklav
 Blågrå svartspik
+Dropptaggsvamp
 Dvärgbägarlav
 Gammelgransskål
-Garnlav
-Granticka
-Gränsticka
 Grå blåbärsfältmätare
-Järpe
 Knottrig blåslav
 Kolflarnlav
 Koralltaggsvamp
 Kortskaftad ärgspik
-Leptoporus mollis
+Kötticka
+Lavskrika
 Mörk kolflarnlav
 Nordtagging
 Rosenticka
 Rödbrun blekspik
+Talltagel
 Talltita
 Tretåig hackspett
 Ullticka
@@ -1107,7 +1189,6 @@
 Blodticka
 Bronshjon
 Bårdlav
-Dropptaggsvamp
 Norrlandslav
 Nästlav
 Plattlummer
@@ -1115,40 +1196,40 @@
 Spindelblomster
 Vedticka
 Vågbandad barkbock
-Lavskrika
+Järpe
 Tjäder
 Vanlig groda
 Vanlig padda
 Fläcknycklar
-Lopplummer
+Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="S5">
+      <c r="V5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Stenberget-Klockartjärnen artfynd.xlsx", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
-      <c r="T5">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Stenberget-Klockartjärnen karta.png", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
-      <c r="V5">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Stenberget-Klockartjärnen FSC-klagomål.docx", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
-      <c r="W5">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Stenberget-Klockartjärnen FSC-klagomål mail.docx", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Stenberget-Klockartjärnen tillsynsbegäran.docx", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Stenberget-Klockartjärnen tillsynsbegäran mail.docx", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Stenberget-Klockartjärnen prioriterade fågelarter.docx", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
@@ -1161,78 +1242,97 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>45508</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Norrbottens län</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Arvidsjaur</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>176.6</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>28</v>
       </c>
       <c r="K6" t="n">
         <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>48</v>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
+        <v>38</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="n">
+        <v>362</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Fläckporing
+Garnlav
 Gräddporing
+Mospindling
+Skrovlig taggsvamp
 Smalfotad taggsvamp
 Tajgataggsvamp
 Tallgråticka
 Blanksvart spiklav
 Blå taggsvamp
 Blågrå svartspik
+Dropptaggsvamp
 Dvärgbägarlav
 Gammelgransskål
-Garnlav
 Grå blåbärsfältmätare
 Hornvaxskinn
 Knottrig blåslav
 Kolflarnlav
 Kortskaftad ärgspik
+Lavskrika
 Liten svartspik
 Mörk kolflarnlav
 Nordtagging
 Reliktbock
 Rosenticka
-Skrovlig taggsvamp
-Spillkråka
+Skarp dropptaggsvamp
 Svartvit taggsvamp
+Talltagel
 Talltaggsvamp
 Tretåig hackspett
 Ullticka
@@ -1243,46 +1343,44 @@
 Vitgrynig nållav
 Vitplätt
 Bronshjon
-Dropptaggsvamp
 Norrlandslav
 Nästlav
 Plattlummer
-Skarp dropptaggsvamp
 Spindelblomster
 Vedticka
+Mattlummer
+Spillkråka
+Tjäder
 Kungsfågel
-Lavskrika
-Tjäder
-Lopplummer
-Mattlummer
+Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="S6">
+      <c r="V6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Suddiesjávrrie artfynd.xlsx", "Suddiesjávrrie")</f>
         <v/>
       </c>
-      <c r="T6">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Suddiesjávrrie karta.png", "Suddiesjávrrie")</f>
         <v/>
       </c>
-      <c r="V6">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Suddiesjávrrie FSC-klagomål.docx", "Suddiesjávrrie")</f>
         <v/>
       </c>
-      <c r="W6">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Suddiesjávrrie FSC-klagomål mail.docx", "Suddiesjávrrie")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Suddiesjávrrie tillsynsbegäran.docx", "Suddiesjávrrie")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Suddiesjávrrie tillsynsbegäran mail.docx", "Suddiesjávrrie")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Suddiesjávrrie prioriterade fågelarter.docx", "Suddiesjávrrie")</f>
         <v/>
       </c>
@@ -1295,73 +1393,95 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>45508</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Norrbottens län</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Arvidsjaur</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>64.7</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>7</v>
       </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>21</v>
-      </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
+        <v>23</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
+        <v>35</v>
+      </c>
+      <c r="R7" t="n">
+        <v>12</v>
+      </c>
+      <c r="S7" t="n">
+        <v>39</v>
+      </c>
+      <c r="T7" t="n">
+        <v>333</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>Phellodon resupinatus
 Fläckporing
+Goliatmusseron
 Gräddporing
+Jättemusseron
 Lateritticka
+Skrovlig taggsvamp
 Smalfotad taggsvamp
+Spadskinn
 Tajgataggsvamp
 Tallgråticka
-Atheta pandionis
+Tornseglare
 Blanksvart spiklav
 Blå taggsvamp
 Blågrå svartspik
+Dropptaggsvamp
 Dvärgbägarlav
 Knottrig blåslav
 Kolflarnlav
+Lavskrika
 Mörk kolflarnlav
 Nordtagging
 Orange taggsvamp
-Skrovlig taggsvamp
-Spillkråka
+Phellodon aquiloniniger
+Skarp dropptaggsvamp
 Svartvit taggsvamp
+Tallriska
 Talltaggsvamp
 Talltita
 Tretåig hackspett
@@ -1370,39 +1490,37 @@
 Vedflamlav
 Vedskivlav
 Vitplätt
-Dropptaggsvamp
 Plattlummer
-Skarp dropptaggsvamp
 Vedticka
-Lavskrika
+Spillkråka
 Tjäder</t>
         </is>
       </c>
-      <c r="S7">
+      <c r="V7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Suöbdieke NÖ artfynd.xlsx", "Suöbdieke NÖ")</f>
         <v/>
       </c>
-      <c r="T7">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Suöbdieke NÖ karta.png", "Suöbdieke NÖ")</f>
         <v/>
       </c>
-      <c r="V7">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Suöbdieke NÖ FSC-klagomål.docx", "Suöbdieke NÖ")</f>
         <v/>
       </c>
-      <c r="W7">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Suöbdieke NÖ FSC-klagomål mail.docx", "Suöbdieke NÖ")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Suöbdieke NÖ tillsynsbegäran.docx", "Suöbdieke NÖ")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Suöbdieke NÖ tillsynsbegäran mail.docx", "Suöbdieke NÖ")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Suöbdieke NÖ prioriterade fågelarter.docx", "Suöbdieke NÖ")</f>
         <v/>
       </c>
@@ -1415,69 +1533,88 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>45508</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Norrbottens län</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Arvidsjaur</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>56.7</v>
       </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
         <v>11</v>
       </c>
-      <c r="J8" t="n">
-        <v>18</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>37</v>
+      </c>
+      <c r="T8" t="n">
+        <v>147</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Fläckporing
+Garnlav
 Gräddporing
 Blanksvart spiklav
 Blå taggsvamp
 Blågrå svartspik
+Dropptaggsvamp
 Dvärgbägarlav
 Gammelgransskål
-Garnlav
-Granticka
 Grå blåbärsfältmätare
 Knottrig blåslav
 Kolflarnlav
 Ladlav
 Mörk kolflarnlav
 Nordtagging
+Rostania effusa
+Skrovellav
+Talltagel
+Tretåig hackspett
 Vedflamlav
 Vedskivlav
 Vedtrappmossa
@@ -1485,7 +1622,6 @@
 Vitgrynig nållav
 Bronshjon
 Bårdlav
-Dropptaggsvamp
 Gullgröppa
 Korallrot
 Luddlav
@@ -1493,35 +1629,36 @@
 Skinnlav
 Spindelblomster
 Stuplav
+Vedticka
 Vågbandad barkbock
-Tjäder</t>
-        </is>
-      </c>
-      <c r="S8">
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="V8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Björnideforsen B artfynd.xlsx", "Björnideforsen B")</f>
         <v/>
       </c>
-      <c r="T8">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Björnideforsen B karta.png", "Björnideforsen B")</f>
         <v/>
       </c>
-      <c r="V8">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Björnideforsen B FSC-klagomål.docx", "Björnideforsen B")</f>
         <v/>
       </c>
-      <c r="W8">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Björnideforsen B FSC-klagomål mail.docx", "Björnideforsen B")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Björnideforsen B tillsynsbegäran.docx", "Björnideforsen B")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Björnideforsen B tillsynsbegäran mail.docx", "Björnideforsen B")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Björnideforsen B prioriterade fågelarter.docx", "Björnideforsen B")</f>
         <v/>
       </c>
@@ -1529,75 +1666,361 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Njuorokvárátj</t>
+          <t>Avvanm 36411</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>45508</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Norrbottens län</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Arvidsjaur</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>11.4</v>
       </c>
       <c r="J9" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
+        <v>28</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>35</v>
+      </c>
+      <c r="T9" t="n">
+        <v>227</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Gräddporing
+Jättemusseron
+Lecidea subhumida
 Smalfotad taggsvamp
-Tallstocksticka
+Tornseglare
+Ulltickeporing
 Blanksvart spiklav
 Blå taggsvamp
 Blågrå svartspik
+Dropptaggsvamp
 Dvärgbägarlav
-Gränsticka
-Hornvaxskinn
-Järpe
+Knottrig blåslav
 Kolflarnlav
 Kortskaftad ärgspik
+Nordtagging
+Svartvit taggsvamp
+Talltagel
+Talltaggsvamp
+Tallticka
+Tretåig hackspett
+Ullticka
+Vaddporing
+Vedflamlav
+Vedskivlav
+Violmussling
+Vitgrynig nållav
+Vitplätt
+Gullgröppa
+Nästlav
+Plattlummer
+Vedticka
+Spillkråka
+Tjäder
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="V9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Avvanm 36411 artfynd.xlsx", "Avvanm 36411")</f>
+        <v/>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Avvanm 36411 karta.png", "Avvanm 36411")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Avvanm 36411 FSC-klagomål.docx", "Avvanm 36411")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Avvanm 36411 FSC-klagomål mail.docx", "Avvanm 36411")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Avvanm 36411 tillsynsbegäran.docx", "Avvanm 36411")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Avvanm 36411 tillsynsbegäran mail.docx", "Avvanm 36411")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Avvanm 36411 prioriterade fågelarter.docx", "Avvanm 36411")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Björnideforsen A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Norrbottens län</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>19</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>23</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>32</v>
+      </c>
+      <c r="T10" t="n">
+        <v>136</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Gräddporing
+Lecidea subhumida
+Smalfotad taggsvamp
+Blanksvart spiklav
+Blå taggsvamp
+Blågrå svartspik
+Dropptaggsvamp
+Dvärgbägarlav
+Knottrig blåslav
+Kolflarnlav
+Liten svartspik
+Mörk kolflarnlav
+Orange taggsvamp
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Talltagel
+Talltaggsvamp
+Tallticka
+Tretåig hackspett
+Vedflamlav
+Vedskivlav
+Vitgrynig nållav
+Bårdlav
+Gullgröppa
+Korallrot
+Källmossa
+Plattlummer
+Spindelblomster
+Trådfräken
+Vedticka
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="V10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Björnideforsen A artfynd.xlsx", "Björnideforsen A")</f>
+        <v/>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Björnideforsen A karta.png", "Björnideforsen A")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Björnideforsen A FSC-klagomål.docx", "Björnideforsen A")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Björnideforsen A FSC-klagomål mail.docx", "Björnideforsen A")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Björnideforsen A tillsynsbegäran.docx", "Björnideforsen A")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Björnideforsen A tillsynsbegäran mail.docx", "Björnideforsen A")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Björnideforsen A prioriterade fågelarter.docx", "Björnideforsen A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Njuorokvárátj</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Norrbottens län</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>20</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>27</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>32</v>
+      </c>
+      <c r="T11" t="n">
+        <v>281</v>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Gräddporing
+Gränsticka
+Skrovlig taggsvamp
+Smalfotad taggsvamp
+Tallstocksticka
+Tornseglare
+Blanksvart spiklav
+Blå taggsvamp
+Blågrå svartspik
+Dropptaggsvamp
+Dvärgbägarlav
+Hornvaxskinn
+Kolflarnlav
+Kortskaftad ärgspik
+Lavskrika
 Mörk kolflarnlav
 Nordtagging
-Skrovlig taggsvamp
-Spillkråka
+Skarp dropptaggsvamp
 Talltaggsvamp
 Talltita
 Tretåig hackspett
@@ -1606,496 +2029,298 @@
 Vedskivlav
 Vedtrappmossa
 Vitplätt
-Dropptaggsvamp
 Gullgröppa
 Plattlummer
-Skarp dropptaggsvamp
 Vedticka
-Lavskrika
-Tjäder</t>
-        </is>
-      </c>
-      <c r="S9">
+Järpe
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="V11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Njuorokvárátj artfynd.xlsx", "Njuorokvárátj")</f>
         <v/>
       </c>
-      <c r="T9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Njuorokvárátj karta.png", "Njuorokvárátj")</f>
         <v/>
       </c>
-      <c r="V9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Njuorokvárátj FSC-klagomål.docx", "Njuorokvárátj")</f>
         <v/>
       </c>
-      <c r="W9">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Njuorokvárátj FSC-klagomål mail.docx", "Njuorokvárátj")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Njuorokvárátj tillsynsbegäran.docx", "Njuorokvárátj")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Njuorokvárátj tillsynsbegäran mail.docx", "Njuorokvárátj")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Njuorokvárátj prioriterade fågelarter.docx", "Njuorokvárátj")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Björnideforsen A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>45508</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gåbddieluoktta</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Norrbottens län</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Arvidsjaur</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
         <v>5</v>
       </c>
-      <c r="I10" t="n">
-        <v>11</v>
-      </c>
-      <c r="J10" t="n">
-        <v>16</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>19</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>31</v>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>Fläckporing
+      <c r="L12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>23</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>30</v>
+      </c>
+      <c r="T12" t="n">
+        <v>138</v>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>Urskogsporing
+Fläckporing
 Gräddporing
+Gränsticka
 Smalfotad taggsvamp
 Blanksvart spiklav
-Blå taggsvamp
 Blågrå svartspik
+Dofttaggsvamp
+Dropptaggsvamp
 Dvärgbägarlav
 Knottrig blåslav
 Kolflarnlav
-Liten svartspik
+Lavskrika
 Mörk kolflarnlav
-Orange taggsvamp
-Svartvit taggsvamp
-Talltaggsvamp
-Tallticka
+Nordtagging
+Skarp dropptaggsvamp
+Talltagel
+Talltita
 Tretåig hackspett
 Vedflamlav
 Vedskivlav
-Vitgrynig nållav
-Bårdlav
-Dropptaggsvamp
+Vitplätt
+Älg
 Gullgröppa
-Korallrot
-Källmossa
+Luddlav
 Plattlummer
-Skarp dropptaggsvamp
 Spindelblomster
-Trådfräken
 Vedticka
-Ögonpyrola
+Spillkråka
 Tjäder</t>
         </is>
       </c>
-      <c r="S10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Björnideforsen A artfynd.xlsx", "Björnideforsen A")</f>
-        <v/>
-      </c>
-      <c r="T10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Björnideforsen A karta.png", "Björnideforsen A")</f>
-        <v/>
-      </c>
-      <c r="V10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Björnideforsen A FSC-klagomål.docx", "Björnideforsen A")</f>
-        <v/>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Björnideforsen A FSC-klagomål mail.docx", "Björnideforsen A")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Björnideforsen A tillsynsbegäran.docx", "Björnideforsen A")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Björnideforsen A tillsynsbegäran mail.docx", "Björnideforsen A")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Björnideforsen A prioriterade fågelarter.docx", "Björnideforsen A")</f>
+      <c r="V12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Gåbddieluoktta artfynd.xlsx", "Gåbddieluoktta")</f>
+        <v/>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Gåbddieluoktta karta.png", "Gåbddieluoktta")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Gåbddieluoktta FSC-klagomål.docx", "Gåbddieluoktta")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Gåbddieluoktta FSC-klagomål mail.docx", "Gåbddieluoktta")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Gåbddieluoktta tillsynsbegäran.docx", "Gåbddieluoktta")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Gåbddieluoktta tillsynsbegäran mail.docx", "Gåbddieluoktta")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Gåbddieluoktta prioriterade fågelarter.docx", "Gåbddieluoktta")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Avvanm 36411</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>45508</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Láttakjávrátje</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Norrbottens län</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Arvidsjaur</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>20</v>
+      </c>
+      <c r="M13" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>25</v>
+      </c>
+      <c r="R13" t="n">
         <v>5</v>
       </c>
-      <c r="J11" t="n">
-        <v>18</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>23</v>
-      </c>
-      <c r="P11" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>30</v>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Fläckporing
-Gräddporing
-Smalfotad taggsvamp
-Ulltickeporing
-Blanksvart spiklav
-Blå taggsvamp
-Blågrå svartspik
-Dvärgbägarlav
-Knottrig blåslav
-Kolflarnlav
-Kortskaftad ärgspik
-Nordtagging
-Spillkråka
-Svart taggsvamp
-Svartvit taggsvamp
-Tallticka
-Ullticka
-Vaddporing
-Vedflamlav
-Vedskivlav
-Violmussling
-Vitplätt
-Dropptaggsvamp
-Gullgröppa
-Nästlav
-Plattlummer
-Vedticka
-Tjäder
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="S11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Avvanm 36411 artfynd.xlsx", "Avvanm 36411")</f>
-        <v/>
-      </c>
-      <c r="T11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Avvanm 36411 karta.png", "Avvanm 36411")</f>
-        <v/>
-      </c>
-      <c r="V11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Avvanm 36411 FSC-klagomål.docx", "Avvanm 36411")</f>
-        <v/>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Avvanm 36411 FSC-klagomål mail.docx", "Avvanm 36411")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Avvanm 36411 tillsynsbegäran.docx", "Avvanm 36411")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Avvanm 36411 tillsynsbegäran mail.docx", "Avvanm 36411")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Avvanm 36411 prioriterade fågelarter.docx", "Avvanm 36411")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Láttakjávrátje</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>45508</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>21</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>26</v>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="S13" t="n">
+        <v>27</v>
+      </c>
+      <c r="T13" t="n">
+        <v>254</v>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Gräddporing
+Lecidea subhumida
 Smalfotad taggsvamp
 Spadskinn
 Blanksvart spiklav
 Blå taggsvamp
 Blågrå svartspik
+Dropptaggsvamp
 Dvärgbägarlav
 Kolflarnlav
 Kortskaftad ärgspik
+Lavskrika
 Mjölsvärting
 Nordlig nållav
 Nordtagging
 Orange taggsvamp
-Spillkråka
+Skarp dropptaggsvamp
 Tallriska
+Talltagel
 Talltaggsvamp
 Talltita
 Vedflamlav
 Vedskivlav
 Vitplätt
-Dropptaggsvamp
-Skarp dropptaggsvamp
 Vedticka
-Lavskrika
-Tjäder</t>
-        </is>
-      </c>
-      <c r="S12">
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="V13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Láttakjávrátje artfynd.xlsx", "Láttakjávrátje")</f>
         <v/>
       </c>
-      <c r="T12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Láttakjávrátje karta.png", "Láttakjávrátje")</f>
         <v/>
       </c>
-      <c r="V12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Láttakjávrátje FSC-klagomål.docx", "Láttakjávrátje")</f>
         <v/>
       </c>
-      <c r="W12">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Láttakjávrátje FSC-klagomål mail.docx", "Láttakjávrátje")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Láttakjávrátje tillsynsbegäran.docx", "Láttakjávrátje")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Láttakjávrátje tillsynsbegäran mail.docx", "Láttakjávrátje")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Láttakjávrátje prioriterade fågelarter.docx", "Láttakjávrátje")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Gåbddieluoktta</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>45508</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>16</v>
-      </c>
-      <c r="P13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>24</v>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>Urskogsporing
-Fläckporing
-Gräddporing
-Smalfotad taggsvamp
-Blanksvart spiklav
-Blågrå svartspik
-Dvärgbägarlav
-Gränsticka
-Knottrig blåslav
-Mörk kolflarnlav
-Spillkråka
-Talltita
-Tretåig hackspett
-Vedflamlav
-Vedskivlav
-Vitplätt
-Dropptaggsvamp
-Gullgröppa
-Luddlav
-Plattlummer
-Skarp dropptaggsvamp
-Spindelblomster
-Vedticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="S13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/artfynd/Gåbddieluoktta artfynd.xlsx", "Gåbddieluoktta")</f>
-        <v/>
-      </c>
-      <c r="T13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Gåbddieluoktta karta.png", "Gåbddieluoktta")</f>
-        <v/>
-      </c>
-      <c r="V13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Gåbddieluoktta FSC-klagomål.docx", "Gåbddieluoktta")</f>
-        <v/>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Gåbddieluoktta FSC-klagomål mail.docx", "Gåbddieluoktta")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Gåbddieluoktta tillsynsbegäran.docx", "Gåbddieluoktta")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Gåbddieluoktta tillsynsbegäran mail.docx", "Gåbddieluoktta")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Gåbddieluoktta prioriterade fågelarter.docx", "Gåbddieluoktta")</f>
         <v/>
       </c>
     </row>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -1591,7 +1591,7 @@
         <v>37</v>
       </c>
       <c r="T8" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>35</v>
       </c>
       <c r="T9" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -542,30 +542,35 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>Geotifflänk</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>Knärotsbuffertlänk</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Klagomålslänk</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Klagomålsmaillänk</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Tillsynsbegäranslänk</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Tillsynsbegäransmaillänk</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
         </is>
@@ -725,26 +730,30 @@
         <v/>
       </c>
       <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor_geotiff/Östra Luspenåivve georefererad karta.tif", "Östra Luspenåivve")</f>
+        <v/>
+      </c>
+      <c r="Y2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/knärot/Östra Luspenåivve karta knärot.png", "Östra Luspenåivve")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Z2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Östra Luspenåivve FSC-klagomål.docx", "Östra Luspenåivve")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Östra Luspenåivve FSC-klagomål mail.docx", "Östra Luspenåivve")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Östra Luspenåivve tillsynsbegäran.docx", "Östra Luspenåivve")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Östra Luspenåivve tillsynsbegäran mail.docx", "Östra Luspenåivve")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Östra Luspenåivve prioriterade fågelarter.docx", "Östra Luspenåivve")</f>
         <v/>
       </c>
@@ -895,26 +904,30 @@
         <v/>
       </c>
       <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor_geotiff/Björnideforsen C georefererad karta.tif", "Björnideforsen C")</f>
+        <v/>
+      </c>
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/knärot/Björnideforsen C karta knärot.png", "Björnideforsen C")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Björnideforsen C FSC-klagomål.docx", "Björnideforsen C")</f>
         <v/>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Björnideforsen C FSC-klagomål mail.docx", "Björnideforsen C")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Björnideforsen C tillsynsbegäran.docx", "Björnideforsen C")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Björnideforsen C tillsynsbegäran mail.docx", "Björnideforsen C")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Björnideforsen C prioriterade fågelarter.docx", "Björnideforsen C")</f>
         <v/>
       </c>
@@ -1057,26 +1070,30 @@
         <v/>
       </c>
       <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor_geotiff/Slaktarberget georefererad karta.tif", "Slaktarberget")</f>
+        <v/>
+      </c>
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/knärot/Slaktarberget karta knärot.png", "Slaktarberget")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Slaktarberget FSC-klagomål.docx", "Slaktarberget")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Slaktarberget FSC-klagomål mail.docx", "Slaktarberget")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Slaktarberget tillsynsbegäran.docx", "Slaktarberget")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Slaktarberget tillsynsbegäran mail.docx", "Slaktarberget")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Slaktarberget prioriterade fågelarter.docx", "Slaktarberget")</f>
         <v/>
       </c>
@@ -1213,23 +1230,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Stenberget-Klockartjärnen karta.png", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor_geotiff/Stenberget-Klockartjärnen georefererad karta.tif", "Stenberget-Klockartjärnen")</f>
+        <v/>
+      </c>
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Stenberget-Klockartjärnen FSC-klagomål.docx", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Stenberget-Klockartjärnen FSC-klagomål mail.docx", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Stenberget-Klockartjärnen tillsynsbegäran.docx", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Stenberget-Klockartjärnen tillsynsbegäran mail.docx", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Stenberget-Klockartjärnen prioriterade fågelarter.docx", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
@@ -1364,23 +1385,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Suddiesjávrrie karta.png", "Suddiesjávrrie")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor_geotiff/Suddiesjávrrie georefererad karta.tif", "Suddiesjávrrie")</f>
+        <v/>
+      </c>
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Suddiesjávrrie FSC-klagomål.docx", "Suddiesjávrrie")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Suddiesjávrrie FSC-klagomål mail.docx", "Suddiesjávrrie")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Suddiesjávrrie tillsynsbegäran.docx", "Suddiesjávrrie")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Suddiesjávrrie tillsynsbegäran mail.docx", "Suddiesjávrrie")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Suddiesjávrrie prioriterade fågelarter.docx", "Suddiesjávrrie")</f>
         <v/>
       </c>
@@ -1504,23 +1529,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Suöbdieke NÖ karta.png", "Suöbdieke NÖ")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor_geotiff/Suöbdieke NÖ georefererad karta.tif", "Suöbdieke NÖ")</f>
+        <v/>
+      </c>
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Suöbdieke NÖ FSC-klagomål.docx", "Suöbdieke NÖ")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Suöbdieke NÖ FSC-klagomål mail.docx", "Suöbdieke NÖ")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Suöbdieke NÖ tillsynsbegäran.docx", "Suöbdieke NÖ")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Suöbdieke NÖ tillsynsbegäran mail.docx", "Suöbdieke NÖ")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Suöbdieke NÖ prioriterade fågelarter.docx", "Suöbdieke NÖ")</f>
         <v/>
       </c>
@@ -1642,23 +1671,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Björnideforsen B karta.png", "Björnideforsen B")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor_geotiff/Björnideforsen B georefererad karta.tif", "Björnideforsen B")</f>
+        <v/>
+      </c>
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Björnideforsen B FSC-klagomål.docx", "Björnideforsen B")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Björnideforsen B FSC-klagomål mail.docx", "Björnideforsen B")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Björnideforsen B tillsynsbegäran.docx", "Björnideforsen B")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Björnideforsen B tillsynsbegäran mail.docx", "Björnideforsen B")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Björnideforsen B prioriterade fågelarter.docx", "Björnideforsen B")</f>
         <v/>
       </c>
@@ -1778,23 +1811,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Avvanm 36411 karta.png", "Avvanm 36411")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor_geotiff/Avvanm 36411 georefererad karta.tif", "Avvanm 36411")</f>
+        <v/>
+      </c>
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Avvanm 36411 FSC-klagomål.docx", "Avvanm 36411")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Avvanm 36411 FSC-klagomål mail.docx", "Avvanm 36411")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Avvanm 36411 tillsynsbegäran.docx", "Avvanm 36411")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Avvanm 36411 tillsynsbegäran mail.docx", "Avvanm 36411")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Avvanm 36411 prioriterade fågelarter.docx", "Avvanm 36411")</f>
         <v/>
       </c>
@@ -1911,23 +1948,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Björnideforsen A karta.png", "Björnideforsen A")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor_geotiff/Björnideforsen A georefererad karta.tif", "Björnideforsen A")</f>
+        <v/>
+      </c>
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Björnideforsen A FSC-klagomål.docx", "Björnideforsen A")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Björnideforsen A FSC-klagomål mail.docx", "Björnideforsen A")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Björnideforsen A tillsynsbegäran.docx", "Björnideforsen A")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Björnideforsen A tillsynsbegäran mail.docx", "Björnideforsen A")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Björnideforsen A prioriterade fågelarter.docx", "Björnideforsen A")</f>
         <v/>
       </c>
@@ -2044,23 +2085,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Njuorokvárátj karta.png", "Njuorokvárátj")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor_geotiff/Njuorokvárátj georefererad karta.tif", "Njuorokvárátj")</f>
+        <v/>
+      </c>
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Njuorokvárátj FSC-klagomål.docx", "Njuorokvárátj")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Njuorokvárátj FSC-klagomål mail.docx", "Njuorokvárátj")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Njuorokvárátj tillsynsbegäran.docx", "Njuorokvárátj")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Njuorokvárátj tillsynsbegäran mail.docx", "Njuorokvárátj")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Njuorokvárátj prioriterade fågelarter.docx", "Njuorokvárátj")</f>
         <v/>
       </c>
@@ -2175,23 +2220,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Gåbddieluoktta karta.png", "Gåbddieluoktta")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor_geotiff/Gåbddieluoktta georefererad karta.tif", "Gåbddieluoktta")</f>
+        <v/>
+      </c>
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Gåbddieluoktta FSC-klagomål.docx", "Gåbddieluoktta")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Gåbddieluoktta FSC-klagomål mail.docx", "Gåbddieluoktta")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Gåbddieluoktta tillsynsbegäran.docx", "Gåbddieluoktta")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Gåbddieluoktta tillsynsbegäran mail.docx", "Gåbddieluoktta")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Gåbddieluoktta prioriterade fågelarter.docx", "Gåbddieluoktta")</f>
         <v/>
       </c>
@@ -2303,23 +2352,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor/Láttakjávrátje karta.png", "Láttakjávrátje")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/kartor_geotiff/Láttakjávrátje georefererad karta.tif", "Láttakjávrátje")</f>
+        <v/>
+      </c>
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomål/Láttakjávrátje FSC-klagomål.docx", "Láttakjávrátje")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/klagomålsmail/Láttakjávrátje FSC-klagomål mail.docx", "Láttakjávrátje")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsyn/Láttakjávrátje tillsynsbegäran.docx", "Láttakjávrátje")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/tillsynsmail/Láttakjávrátje tillsynsbegäran mail.docx", "Láttakjávrátje")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Láttakjávrátje prioriterade fågelarter.docx", "Láttakjávrátje")</f>
         <v/>
       </c>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AO13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -573,6 +573,61 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Markägare</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Prio</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Naturtyp_</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Intresse</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Avsatt omr</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>LST_bevak</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>NV/Klass</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Avvanm_</t>
         </is>
       </c>
     </row>
@@ -757,6 +812,44 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Östra Luspenåivve prioriterade fågelarter.docx", "Östra Luspenåivve")</f>
         <v/>
       </c>
+      <c r="AE2" t="n">
+        <v/>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>SCA + Sveaskog</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Inventerad av SNF 2023</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v/>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>högintressant</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v/>
+      </c>
+      <c r="AM2" t="n">
+        <v/>
+      </c>
+      <c r="AN2" t="n">
+        <v/>
+      </c>
+      <c r="AO2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -931,6 +1024,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Björnideforsen C prioriterade fågelarter.docx", "Björnideforsen C")</f>
         <v/>
       </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre skog i ekopark PG/PF/NS.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v/>
+      </c>
+      <c r="AL3" t="n">
+        <v/>
+      </c>
+      <c r="AM3" t="n">
+        <v/>
+      </c>
+      <c r="AN3" t="n">
+        <v/>
+      </c>
+      <c r="AO3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -1097,6 +1226,48 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Slaktarberget prioriterade fågelarter.docx", "Slaktarberget")</f>
         <v/>
       </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Domstol fattat interimistiskt beslut att stoppa avv 150724</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>intressant</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v/>
+      </c>
+      <c r="AM4" t="n">
+        <v/>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Höga naturvärden klass 2.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>A 29088-2023, inkom 230628</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -1254,6 +1425,46 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Stenberget-Klockartjärnen prioriterade fågelarter.docx", "Stenberget-Klockartjärnen")</f>
         <v/>
       </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>högintressant</t>
+        </is>
+      </c>
+      <c r="AL5" t="n">
+        <v/>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Hela området inom LST bevakskikt</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Mycket höga naturvärden. klass 1.</t>
+        </is>
+      </c>
+      <c r="AO5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -1409,6 +1620,46 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Suddiesjávrrie prioriterade fågelarter.docx", "Suddiesjávrrie")</f>
         <v/>
       </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>1 nybrgr</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Tallskog med hög ålder. Avv.anm. i Ö</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v/>
+      </c>
+      <c r="AL6" t="n">
+        <v/>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>ca 50%</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v/>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>A 34531-2023, inkom 230802</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -1553,6 +1804,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Suöbdieke NÖ prioriterade fågelarter.docx", "Suöbdieke NÖ")</f>
         <v/>
       </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
+      </c>
+      <c r="AJ7" t="n">
+        <v/>
+      </c>
+      <c r="AL7" t="n">
+        <v/>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>PF el PG klassat</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v/>
+      </c>
+      <c r="AO7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -1695,6 +1982,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Björnideforsen B prioriterade fågelarter.docx", "Björnideforsen B")</f>
         <v/>
       </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre skog i ekopark PG/PF/NS.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v/>
+      </c>
+      <c r="AL8" t="n">
+        <v/>
+      </c>
+      <c r="AM8" t="n">
+        <v/>
+      </c>
+      <c r="AN8" t="n">
+        <v/>
+      </c>
+      <c r="AO8" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -1835,6 +2158,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Avvanm 36411 prioriterade fågelarter.docx", "Avvanm 36411")</f>
         <v/>
       </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
+      </c>
+      <c r="AJ9" t="n">
+        <v/>
+      </c>
+      <c r="AL9" t="n">
+        <v/>
+      </c>
+      <c r="AM9" t="n">
+        <v/>
+      </c>
+      <c r="AN9" t="n">
+        <v/>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>A 36411-2023, inkom 230814</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -1972,6 +2331,46 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Björnideforsen A prioriterade fågelarter.docx", "Björnideforsen A")</f>
         <v/>
       </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre skog i ekopark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>intressant</t>
+        </is>
+      </c>
+      <c r="AL10" t="n">
+        <v/>
+      </c>
+      <c r="AM10" t="n">
+        <v/>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Höga naturvärden klass 2.</t>
+        </is>
+      </c>
+      <c r="AO10" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -2109,6 +2508,46 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Njuorokvárátj prioriterade fågelarter.docx", "Njuorokvárátj")</f>
         <v/>
       </c>
+      <c r="AE11" t="n">
+        <v/>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Avverkat +150-årig skog i ekoparken. Ansl. skog intressant.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>högintressant</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Ekopark</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v/>
+      </c>
+      <c r="AN11" t="n">
+        <v/>
+      </c>
+      <c r="AO11" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -2244,6 +2683,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Gåbddieluoktta prioriterade fågelarter.docx", "Gåbddieluoktta")</f>
         <v/>
       </c>
+      <c r="AE12" t="n">
+        <v/>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v/>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Endast NB = FA, hög ålder.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v/>
+      </c>
+      <c r="AL12" t="n">
+        <v/>
+      </c>
+      <c r="AM12" t="n">
+        <v/>
+      </c>
+      <c r="AN12" t="n">
+        <v/>
+      </c>
+      <c r="AO12" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2376,6 +2851,44 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2024/fåglar/Láttakjávrátje prioriterade fågelarter.docx", "Láttakjávrátje")</f>
         <v/>
       </c>
+      <c r="AE13" t="n">
+        <v/>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Torr tallskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v/>
+      </c>
+      <c r="AL13" t="n">
+        <v/>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Hela området inom LST bevak</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v/>
+      </c>
+      <c r="AO13" t="n">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -643,10 +643,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
